--- a/measurements/37/Filled_2D_sections/axial/week37_axial_Batch_Allmarks.xlsx
+++ b/measurements/37/Filled_2D_sections/axial/week37_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +616,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13.99256395002974</v>
+        <v>5333.673469387754</v>
       </c>
       <c r="D2" t="n">
-        <v>36.20985953691529</v>
+        <v>706.9544004826319</v>
       </c>
       <c r="E2" t="n">
-        <v>16.69570601277235</v>
+        <v>325.9637840588887</v>
       </c>
       <c r="F2" t="n">
         <v>2.168812718025488</v>
@@ -525,24 +635,60 @@
         <v>0.1341076289584889</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6059451219512195</v>
+        <v>2.001488095238095</v>
       </c>
       <c r="J2" t="n">
-        <v>2.346036585365854</v>
+        <v>45.80357142857142</v>
       </c>
       <c r="K2" t="n">
-        <v>1.346250952743902</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>10.14009021577381</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>45.80357142857142</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33.81324404761904</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>6.5625</v>
+      </c>
+      <c r="X2" t="n">
+        <v>13.68861607142857</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.259052579365079</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.001488095238095</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4.981398809523809</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.3837890625</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>14.06756395002975</v>
+      <c r="AK2" s="2" t="n">
+        <v>5362.261904761905</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +699,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.33878643664485</v>
+        <v>5465.646258503401</v>
       </c>
       <c r="D3" t="n">
-        <v>35.03912780343033</v>
+        <v>684.097257114592</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70060867798038</v>
+        <v>326.0595027605692</v>
       </c>
       <c r="F3" t="n">
         <v>2.098074895295831</v>
@@ -572,24 +718,60 @@
         <v>0.1467626977081297</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6161394817073171</v>
+        <v>1.6796875</v>
       </c>
       <c r="J3" t="n">
-        <v>2.29639862804878</v>
+        <v>44.83444940476191</v>
       </c>
       <c r="K3" t="n">
-        <v>1.336961699695122</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>9.848214285714285</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>44.83444940476191</v>
+      </c>
+      <c r="N3" t="n">
+        <v>33.76116071428572</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5.280877976190476</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13.78534226190476</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.825520833333332</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.6796875</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4.815848214285714</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>31.1380043381598</v>
+      <c r="AK3" s="2" t="n">
+        <v>607.9324656497864</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +782,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14.32867340868531</v>
+        <v>5461.791383219955</v>
       </c>
       <c r="D4" t="n">
-        <v>35.33324672536153</v>
+        <v>689.839578923725</v>
       </c>
       <c r="E4" t="n">
-        <v>16.69469062584202</v>
+        <v>325.9439598378681</v>
       </c>
       <c r="F4" t="n">
         <v>2.116436148308644</v>
@@ -619,24 +801,60 @@
         <v>0.1442277259371111</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6796875</v>
+        <v>2.053571428571428</v>
       </c>
       <c r="J4" t="n">
-        <v>2.20750762195122</v>
+        <v>43.09895833333333</v>
       </c>
       <c r="K4" t="n">
-        <v>1.329935213414634</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>11.13810668498168</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>43.09895833333333</v>
+      </c>
+      <c r="N4" t="n">
+        <v>33.29241071428572</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5.710565476190476</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14.20014880952381</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.294084821428571</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.053571428571428</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.271949404761905</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.527901785714286</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>16.4540010933469</v>
+      <c r="AK4" s="2" t="n">
+        <v>321.2447832510585</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +865,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.98483045806068</v>
+        <v>5330.725623582766</v>
       </c>
       <c r="D5" t="n">
-        <v>35.36182164273611</v>
+        <v>690.3974701677049</v>
       </c>
       <c r="E5" t="n">
-        <v>16.96124994173283</v>
+        <v>331.1482131481171</v>
       </c>
       <c r="F5" t="n">
         <v>2.084859415680741</v>
@@ -666,23 +884,59 @@
         <v>0.1405393080760402</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7241806402439025</v>
+        <v>2.373511904761905</v>
       </c>
       <c r="J5" t="n">
-        <v>2.27000762195122</v>
+        <v>44.31919642857142</v>
       </c>
       <c r="K5" t="n">
-        <v>1.351824504573171</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>12.71236359126984</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44.31919642857142</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32.87202380952381</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6.473214285714286</v>
+      </c>
+      <c r="X5" t="n">
+        <v>14.24107142857143</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.560214710884352</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.526785714285714</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.535342261904762</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.373511904761905</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.889590544772649</v>
       </c>
     </row>
@@ -694,42 +948,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.6918500892326</v>
+        <v>5219.047619047618</v>
       </c>
       <c r="D6" t="n">
-        <v>35.12527328875007</v>
+        <v>685.7791451613108</v>
       </c>
       <c r="E6" t="n">
-        <v>17.2371940816321</v>
+        <v>336.535693974722</v>
       </c>
       <c r="F6" t="n">
-        <v>2.037760503386072</v>
+        <v>2.037760503386073</v>
       </c>
       <c r="G6" t="n">
         <v>0.1394545137248482</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7097942073170732</v>
+        <v>1.744791666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>2.300971798780488</v>
+        <v>44.92373511904761</v>
       </c>
       <c r="K6" t="n">
-        <v>1.352086509146341</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>11.09800170068027</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>44.92373511904761</v>
+      </c>
+      <c r="N6" t="n">
+        <v>32.19866071428572</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.770089285714286</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14.61123511904762</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.077115221088436</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.744791666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.941964285714286</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.1899152879627549</v>
       </c>
     </row>
@@ -741,17 +1031,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13.88518738845925</v>
+        <v>5292.743764172335</v>
       </c>
       <c r="D7" t="n">
-        <v>32.67297676132947</v>
+        <v>637.9009748640514</v>
       </c>
       <c r="E7" t="n">
-        <v>17.24066079535136</v>
+        <v>336.6033774330502</v>
       </c>
       <c r="F7" t="n">
         <v>1.895111628792045</v>
@@ -760,24 +1050,60 @@
         <v>0.1634497277209546</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7087461890243902</v>
+        <v>1.625744047619047</v>
       </c>
       <c r="J7" t="n">
-        <v>2.251143292682927</v>
+        <v>43.95089285714285</v>
       </c>
       <c r="K7" t="n">
-        <v>1.322479992378049</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>10.34956951530612</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>43.95089285714285</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31.24813988095238</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5.647321428571428</v>
+      </c>
+      <c r="X7" t="n">
+        <v>14.24293154761905</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.757130456349206</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.625744047619047</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4.810267857142857</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.858692956349207</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3.45</v>
+      <c r="AK7" s="2" t="n">
+        <v>16.3</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1114,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.95895300416419</v>
+        <v>5320.861678004535</v>
       </c>
       <c r="D8" t="n">
-        <v>31.69736704593751</v>
+        <v>618.853356611161</v>
       </c>
       <c r="E8" t="n">
-        <v>17.04553888483745</v>
+        <v>332.793854418255</v>
       </c>
       <c r="F8" t="n">
-        <v>1.859569665710794</v>
+        <v>1.859569665710793</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1745887804726513</v>
+        <v>0.1745887804726514</v>
       </c>
       <c r="H8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.085193452380952</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.71391369047619</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.616443452380956</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>42.71391369047619</v>
+      </c>
+      <c r="N8" t="n">
+        <v>29.84933035714285</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.6766387195121951</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.187785823170732</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.268935785060976</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="n">
+        <v>8.232886904761905</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13.32403273809524</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>11.07933407738095</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.085193452380952</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4.486607142857142</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.040674603174603</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.8850705030487805</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.93071056547619</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1197,79 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.17608566329566</v>
+        <v>5403.628117913831</v>
       </c>
       <c r="D9" t="n">
-        <v>31.53082002663031</v>
+        <v>615.6017243294489</v>
       </c>
       <c r="E9" t="n">
-        <v>17.1441152183021</v>
+        <v>334.7184399763743</v>
       </c>
       <c r="F9" t="n">
         <v>1.839162862891272</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1791825288540721</v>
+        <v>0.179182528854072</v>
       </c>
       <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.530877976190476</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40.55059523809523</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.29985119047619</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>40.55059523809523</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23.62723214285714</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.6319550304878049</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.076981707317073</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.141029916158537</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="n">
+        <v>5.591517857142857</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12.59300595238095</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.142485119047619</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.530877976190476</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>4.90141369047619</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.204985119047619</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>2.001300495426829</v>
+      <c r="AK9" s="2" t="n">
+        <v>38.24116443452381</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1280,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14.22903033908388</v>
+        <v>5423.809523809524</v>
       </c>
       <c r="D10" t="n">
-        <v>29.90373034012027</v>
+        <v>583.8347352118719</v>
       </c>
       <c r="E10" t="n">
-        <v>17.13227907913487</v>
+        <v>334.487353449776</v>
       </c>
       <c r="F10" t="n">
         <v>1.74546131323179</v>
@@ -901,24 +1299,60 @@
         <v>0.1999559970129109</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6832126524390244</v>
+        <v>1.871279761904762</v>
       </c>
       <c r="J10" t="n">
-        <v>1.877762957317073</v>
+        <v>36.66108630952381</v>
       </c>
       <c r="K10" t="n">
-        <v>1.110851753048781</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>8.220522584033613</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>36.66108630952381</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.00223214285714</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5.405505952380952</v>
+      </c>
+      <c r="X10" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.565538194444443</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.871279761904762</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>4.401041666666666</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.188037367724867</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.343717050940041</v>
+      <c r="AK10" s="2" t="n">
+        <v>8.756128021370808</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1363,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14.30874479476502</v>
+        <v>5454.195011337868</v>
       </c>
       <c r="D11" t="n">
-        <v>28.6438070681037</v>
+        <v>559.2362332344055</v>
       </c>
       <c r="E11" t="n">
-        <v>16.86817111329335</v>
+        <v>329.3309598309653</v>
       </c>
       <c r="F11" t="n">
         <v>1.698097966621307</v>
@@ -948,16 +1382,60 @@
         <v>0.2191542625811814</v>
       </c>
       <c r="H11" t="n">
+        <v>17</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.638764880952381</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.77752976190476</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.612591911764706</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>35.77752976190476</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22.97433035714285</v>
+      </c>
+      <c r="S11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.7110327743902439</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.83250762195122</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.111423399390244</v>
+      <c r="W11" t="n">
+        <v>5.111607142857142</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14.16294642857143</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.580078125</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.638764880952381</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.066220238095238</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.940171807359307</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1446,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.46400951814396</v>
+        <v>5513.378684807256</v>
       </c>
       <c r="D12" t="n">
-        <v>32.51826588991212</v>
+        <v>634.8804292792365</v>
       </c>
       <c r="E12" t="n">
-        <v>16.44487015503209</v>
+        <v>321.0665125506264</v>
       </c>
       <c r="F12" t="n">
         <v>1.977410924096692</v>
@@ -987,16 +1465,60 @@
         <v>0.1718873069585438</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7210365853658537</v>
+        <v>2.077752976190476</v>
       </c>
       <c r="J12" t="n">
-        <v>1.829077743902439</v>
+        <v>35.71056547619047</v>
       </c>
       <c r="K12" t="n">
-        <v>1.119736089939025</v>
+        <v>9.420440051020407</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>35.71056547619047</v>
+      </c>
+      <c r="N12" t="n">
+        <v>23.40587797619047</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.990699404761904</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.25223214285714</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.031498015873014</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.077752976190476</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.473586309523809</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.096788194444444</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>38.48854993386243</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1529,82 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.23289708506841</v>
+        <v>5425.283446712017</v>
       </c>
       <c r="D13" t="n">
-        <v>32.99178330200475</v>
+        <v>644.1252930391402</v>
       </c>
       <c r="E13" t="n">
-        <v>16.38772027666976</v>
+        <v>319.9507292111714</v>
       </c>
       <c r="F13" t="n">
-        <v>2.013201515830926</v>
+        <v>2.013201515830925</v>
       </c>
       <c r="G13" t="n">
         <v>0.1643204406866838</v>
       </c>
       <c r="H13" t="n">
+        <v>17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.044270833333333</v>
+      </c>
+      <c r="J13" t="n">
+        <v>36.13839285714285</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.688287815126051</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>36.13839285714285</v>
+      </c>
+      <c r="N13" t="n">
+        <v>24.04203869047619</v>
+      </c>
+      <c r="O13" t="n">
+        <v>14.90699404761905</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.7482850609756098</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.850990853658537</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.148556592987805</v>
+      <c r="W13" t="n">
+        <v>6.484375</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.609375</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.401506696428571</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.044270833333333</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.566592261904762</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.500744047619047</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>28.31943714985994</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1615,82 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14.11302795954789</v>
+        <v>5379.591836734693</v>
       </c>
       <c r="D14" t="n">
-        <v>32.35662159687136</v>
+        <v>631.7245168912978</v>
       </c>
       <c r="E14" t="n">
-        <v>16.65284359455109</v>
+        <v>325.1269463698069</v>
       </c>
       <c r="F14" t="n">
-        <v>1.94300879685549</v>
+        <v>1.943008796855489</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1693962242830013</v>
+        <v>0.1693962242830014</v>
       </c>
       <c r="H14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.330729166666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>36.63318452380952</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.051229866946777</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.9259717987804879</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.876333841463415</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.289991425304878</v>
+      <c r="P14" t="n">
+        <v>18.07849702380952</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>36.63318452380952</v>
+      </c>
+      <c r="R14" t="n">
+        <v>25.185546875</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.684151785714286</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5.824032738095238</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.927455357142857</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.330729166666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.795386904761904</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.469308035714285</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>14.90699404761905</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1701,82 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14.04878048780488</v>
+        <v>5355.102040816326</v>
       </c>
       <c r="D15" t="n">
-        <v>33.80186138792736</v>
+        <v>659.9411032881055</v>
       </c>
       <c r="E15" t="n">
-        <v>16.25668164288125</v>
+        <v>317.3923558848244</v>
       </c>
       <c r="F15" t="n">
         <v>2.079259601096333</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1545137944317757</v>
+        <v>0.1545137944317758</v>
       </c>
       <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.668526785714286</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.39620535714285</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.321521577380949</v>
+      </c>
+      <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.9974275914634146</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.81297637195122</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.300447789634146</v>
+      <c r="P15" t="n">
+        <v>19.47358630952381</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>35.39620535714285</v>
+      </c>
+      <c r="R15" t="n">
+        <v>25.38969494047619</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>5.236235119047619</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6.231398809523809</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.77241443452381</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.668526785714286</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>4.739583333333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.061988467261905</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>18.77604166666666</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1787,79 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14.45806067816776</v>
+        <v>5511.11111111111</v>
       </c>
       <c r="D16" t="n">
-        <v>25.83905225556071</v>
+        <v>504.4767345133282</v>
       </c>
       <c r="E16" t="n">
-        <v>16.16402334992479</v>
+        <v>315.583313022341</v>
       </c>
       <c r="F16" t="n">
-        <v>1.59855326215431</v>
+        <v>1.598553262154311</v>
       </c>
       <c r="G16" t="n">
         <v>0.2721239376731187</v>
       </c>
       <c r="H16" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.69456845238095</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.886598389355743</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>1.025247713414634</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.367282774390244</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.196265243902439</v>
+      <c r="M16" t="n">
+        <v>26.69456845238095</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20.01674107142857</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5.152529761904762</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9.038318452380953</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.031249999999999</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.785714285714286</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>4.090401785714286</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.130373677248677</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>36.01469494047618</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1870,79 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14.34741225461035</v>
+        <v>5468.934240362812</v>
       </c>
       <c r="D17" t="n">
-        <v>26.19235180936209</v>
+        <v>511.3744877065931</v>
       </c>
       <c r="E17" t="n">
-        <v>15.77969754323727</v>
+        <v>308.0798091774895</v>
       </c>
       <c r="F17" t="n">
         <v>1.65987666985337</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2628055003668327</v>
+        <v>0.2628055003668328</v>
       </c>
       <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.975446428571428</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28.64955357142857</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.436569940476192</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>1.384432164634146</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.467416158536585</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.425924161585366</v>
+      <c r="M17" t="n">
+        <v>28.64955357142857</v>
+      </c>
+      <c r="N17" t="n">
+        <v>27.02938988095238</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5.159970238095238</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8.645833333333332</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.85453869047619</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.975446428571428</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3.268229166666667</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.660435267857143</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>25.28762090773809</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1953,79 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.19988102320048</v>
+        <v>5412.698412698413</v>
       </c>
       <c r="D18" t="n">
-        <v>25.27389192581177</v>
+        <v>493.4426518848964</v>
       </c>
       <c r="E18" t="n">
-        <v>15.60131439348547</v>
+        <v>304.5970905394781</v>
       </c>
       <c r="F18" t="n">
         <v>1.61998478386957</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2793510586040692</v>
+        <v>0.2793510586040691</v>
       </c>
       <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.841517857142857</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.38355654761904</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.352120535714285</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>1.401200457317073</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.709889481707317</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.555544969512195</v>
+      <c r="M18" t="n">
+        <v>33.38355654761904</v>
+      </c>
+      <c r="N18" t="n">
+        <v>27.35677083333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5.124627976190476</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.63578869047619</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.075148809523808</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.841517857142857</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>4.4140625</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.000106292517006</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2036,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13.99524092801904</v>
+        <v>5334.69387755102</v>
       </c>
       <c r="D19" t="n">
-        <v>26.0745852807673</v>
+        <v>509.0752364340282</v>
       </c>
       <c r="E19" t="n">
-        <v>15.38252021335974</v>
+        <v>300.3253946417854</v>
       </c>
       <c r="F19" t="n">
         <v>1.695078889486619</v>
@@ -1260,16 +2055,60 @@
         <v>0.2586755754935653</v>
       </c>
       <c r="H19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.519717261904762</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.88467261904762</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.389774659863946</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>1.671589176829268</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.786775914634146</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.729182545731707</v>
+      <c r="M19" t="n">
+        <v>34.88467261904762</v>
+      </c>
+      <c r="N19" t="n">
+        <v>32.63578869047619</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.84375</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.003348214285714</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.68359375</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.519717261904762</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4.23735119047619</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.928695436507936</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>7.684151785714286</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2119,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13.46579417013682</v>
+        <v>5132.879818594104</v>
       </c>
       <c r="D20" t="n">
-        <v>27.6863720969456</v>
+        <v>540.5434552260807</v>
       </c>
       <c r="E20" t="n">
-        <v>15.36823270960552</v>
+        <v>300.0464481399173</v>
       </c>
       <c r="F20" t="n">
         <v>1.801532591294049</v>
@@ -1299,16 +2138,60 @@
         <v>0.2207545852855589</v>
       </c>
       <c r="H20" t="n">
+        <v>18</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.594866071428571</v>
+      </c>
+      <c r="J20" t="n">
+        <v>40.93936011904761</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.789868551587301</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>1.552210365853659</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.096894054878049</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.824552210365854</v>
+      <c r="M20" t="n">
+        <v>40.93936011904761</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30.30505952380952</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.938616071428571</v>
+      </c>
+      <c r="X20" t="n">
+        <v>9.034598214285714</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.03031994047619</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.594866071428571</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>4.453125</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.404327876984127</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.824032738095238</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2202,76 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13.13146936347412</v>
+        <v>5005.442176870748</v>
       </c>
       <c r="D21" t="n">
-        <v>28.50727097871827</v>
+        <v>556.5705286321186</v>
       </c>
       <c r="E21" t="n">
-        <v>15.3219035573122</v>
+        <v>299.1419265951429</v>
       </c>
       <c r="F21" t="n">
         <v>1.860556742971634</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2030541644255594</v>
+        <v>0.2030541644255595</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5266768292682927</v>
+        <v>2.170758928571428</v>
       </c>
       <c r="J21" t="n">
-        <v>2.581269054878049</v>
+        <v>33.75930059523809</v>
       </c>
       <c r="K21" t="n">
-        <v>1.612360264227642</v>
+        <v>5.750393907563025</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>33.75930059523809</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.838169642857142</v>
+      </c>
+      <c r="X21" t="n">
+        <v>10.28273809523809</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.634114583333333</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.170758928571428</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.893229166666667</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.121744791666667</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>4.927455357142857</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2281,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>5.608161027568922</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2303,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>11.85962954260652</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2320,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>8.244996792576679</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>3.526785714285714</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.535342261904762</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>2.373511904761905</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.907405231829574</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>4.370594454887218</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>3.083459425021337</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/37/Filled_2D_sections/axial/week37_axial_Batch_Allmarks.xlsx
+++ b/measurements/37/Filled_2D_sections/axial/week37_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2439,4 +2645,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week37_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5362.261904761905</v>
+      </c>
+      <c r="D10" t="n">
+        <v>127.1859983616561</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5005.442176870748</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5513.378684807256</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>607.9324656497864</v>
+      </c>
+      <c r="D11" t="n">
+        <v>70.56076024563187</v>
+      </c>
+      <c r="E11" t="n">
+        <v>493.4426518848964</v>
+      </c>
+      <c r="F11" t="n">
+        <v>706.9544004826319</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.889590544772648</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1795171306212373</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.598553262154311</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.168812718025488</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1899152879627549</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0473678762593699</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1341076289584889</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2793510586040691</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>17</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>17</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>11</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>17</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>17</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>10</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0177.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0179.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>17</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0181.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0184.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>20</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>14</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0186.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>21</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>21</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0188.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>18</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>18</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>12</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0190.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>17</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>12</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.341839133312916</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6958523739384593</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.213953957333768</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.110254685797663</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>44</v>
+      </c>
+      <c r="C48" t="n">
+        <v>31.62346117424242</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.191473475318107</v>
+      </c>
+      <c r="E48" t="n">
+        <v>14.90699404761905</v>
+      </c>
+      <c r="F48" t="n">
+        <v>45.80357142857142</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>100</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8.273790922619046</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.606873881644537</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.838169642857142</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14.61123511904762</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>182</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.091088598901099</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6364969828729251</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.519717261904762</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.981398809523809</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>